--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY254"/>
+  <dimension ref="A1:AZ254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562855</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124148128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124159621</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124148083</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123563245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1395,6 +1425,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123568788</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1521,6 +1556,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569150</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1648,6 +1688,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569547</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1780,6 +1825,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452547</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1901,6 +1951,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452664</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2028,6 +2083,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452723</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2155,6 +2215,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452758</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2282,6 +2347,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123453868</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2409,6 +2479,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123454880</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2536,6 +2611,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123455365</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2663,6 +2743,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564291</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2785,6 +2870,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564362</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2914,6 +3004,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103808703</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3040,6 +3135,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133065393</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3166,6 +3266,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133065726</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3292,6 +3397,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133066457</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3418,6 +3528,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124254291</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3549,6 +3664,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255029</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3675,6 +3795,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255182</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3801,6 +3926,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255199</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3927,6 +4057,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124255227</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4053,6 +4188,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133066817</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4165,6 +4305,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773496</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4272,6 +4417,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630151</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4379,6 +4529,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123636652</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4486,6 +4641,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661726</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4593,6 +4753,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663941</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4700,6 +4865,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123634401</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4807,6 +4977,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123635051</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4914,6 +5089,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123635312</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5021,6 +5201,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123635849</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5128,6 +5313,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123636182</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5235,6 +5425,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123638441</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5342,6 +5537,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123634138</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5449,6 +5649,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123634648</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5556,6 +5761,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123635424</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5663,6 +5873,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637884</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5770,6 +5985,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665949</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5877,6 +6097,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773738</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5984,6 +6209,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123635775</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6091,6 +6321,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771237</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6198,6 +6433,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773574</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6305,6 +6545,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123774062</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6412,6 +6657,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124117546</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6538,6 +6788,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663973</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6664,6 +6919,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630575</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6776,6 +7036,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771129</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6903,6 +7168,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123628849</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7030,6 +7300,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123629003</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7156,6 +7431,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630058</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7283,6 +7563,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630375</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7410,6 +7695,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630392</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7536,6 +7826,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630440</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7662,6 +7957,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630514</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7788,6 +8088,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630616</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7914,6 +8219,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630752</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8040,6 +8350,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630843</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8166,6 +8481,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630859</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8292,6 +8612,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123630963</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8418,6 +8743,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123631130</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8544,6 +8874,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123631588</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8670,6 +9005,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123631647</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8796,6 +9136,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123631668</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8922,6 +9267,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123631990</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9048,6 +9398,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123632719</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9174,6 +9529,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123632731</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9300,6 +9660,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123632766</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9426,6 +9791,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123632792</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9552,6 +9922,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123632872</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9683,6 +10058,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123634660</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9809,6 +10189,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637179</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9935,6 +10320,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637278</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10061,6 +10451,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637518</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10187,6 +10582,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637534</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10313,6 +10713,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637586</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10439,6 +10844,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637680</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10565,6 +10975,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637942</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10691,6 +11106,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637999</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10817,6 +11237,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123638144</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10943,6 +11368,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123643552</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11069,6 +11499,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123643648</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11195,6 +11630,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123643786</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11321,6 +11761,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661339</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11447,6 +11892,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661642</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11573,6 +12023,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661690</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11695,6 +12150,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661784</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11821,6 +12281,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661791</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11947,6 +12412,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661808</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12073,6 +12543,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661864</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12199,6 +12674,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123661951</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12325,6 +12805,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662010</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12451,6 +12936,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662068</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12577,6 +13067,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662121</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12703,6 +13198,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662241</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12829,6 +13329,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662340</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12955,6 +13460,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662402</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13081,6 +13591,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662567</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13207,6 +13722,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662581</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13329,6 +13849,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662597</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13455,6 +13980,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662866</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13581,6 +14111,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662893</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13707,6 +14242,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662918</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13833,6 +14373,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662939</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13959,6 +14504,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662945</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14085,6 +14635,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123662984</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14211,6 +14766,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663018</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14337,6 +14897,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663064</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14463,6 +15028,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663188</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14589,6 +15159,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663197</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14715,6 +15290,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663251</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14836,6 +15416,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663614</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14962,6 +15547,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663788</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -15088,6 +15678,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123663934</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15214,6 +15809,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664036</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15340,6 +15940,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664080</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -15461,6 +16066,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664091</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15587,6 +16197,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664124</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15713,6 +16328,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664203</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15839,6 +16459,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664231</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15965,6 +16590,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664264</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -16091,6 +16721,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664287</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16217,6 +16852,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664726</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -16348,6 +16988,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664829</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -16470,6 +17115,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664901</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16596,6 +17246,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123664928</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16722,6 +17377,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665171</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16848,6 +17508,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665243</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16974,6 +17639,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665310</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -17100,6 +17770,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665430</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -17226,6 +17901,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665453</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -17352,6 +18032,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123666132</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -17478,6 +18163,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771579</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -17600,6 +18290,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771673</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17722,6 +18417,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771697</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17848,6 +18548,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771973</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17974,6 +18679,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123772119</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -18100,6 +18810,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123772191</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -18226,6 +18941,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123772262</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -18352,6 +19072,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123772853</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -18478,6 +19203,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123772915</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -18604,6 +19334,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773003</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -18730,6 +19465,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773073</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -18856,6 +19596,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773088</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -18982,6 +19727,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773110</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -19108,6 +19858,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773292</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -19234,6 +19989,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773337</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -19360,6 +20120,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123773375</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -19482,6 +20247,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123774116</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -19608,6 +20378,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123774970</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -19734,6 +20509,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123775092</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -19860,6 +20640,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123775117</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -19986,6 +20771,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123775148</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -20112,6 +20902,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123775202</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -20238,6 +21033,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123822818</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -20364,6 +21164,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123822826</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -20490,6 +21295,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123822958</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -20616,6 +21426,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123823230</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -20742,6 +21557,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123823741</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -20868,6 +21688,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124117836</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -20999,6 +21824,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123635209</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -21106,6 +21936,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123636153</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -21232,6 +22067,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123636849</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -21358,6 +22198,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123637127</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -21484,6 +22329,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123638527</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -21610,6 +22460,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123638646</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -21736,6 +22591,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123638752</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -21862,6 +22722,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123571689</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -21993,6 +22858,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123572551</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -22119,6 +22989,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132334883</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -22221,6 +23096,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122853226</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -22328,6 +23208,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820267</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -22429,6 +23314,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122853220</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -22536,6 +23426,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128295608</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -22643,6 +23538,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128824944</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -22774,6 +23674,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820310</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -22900,6 +23805,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126223335</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -23021,6 +23931,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124776567</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -23152,6 +24067,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128956949</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -23278,6 +24198,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129457818</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -23399,6 +24324,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764125</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -23525,6 +24455,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132741713</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -23637,6 +24572,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123246033</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -23744,6 +24684,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122827482</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -23851,6 +24796,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122827770</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -23952,6 +24902,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122853672</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -24053,6 +25008,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122853678</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -24154,6 +25114,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122853683</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -24261,6 +25226,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122826361</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -24368,6 +25338,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122827273</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -24475,6 +25450,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122827376</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -24582,6 +25562,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122826109</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -24689,6 +25674,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122828141</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -24796,6 +25786,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124505050</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -24903,6 +25898,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124505147</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -25029,6 +26029,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124502716</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -25155,6 +26160,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124502759</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -25281,6 +26291,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124502785</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -25407,6 +26422,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124502909</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -25533,6 +26553,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503058</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -25659,6 +26684,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503101</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -25785,6 +26815,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503372</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -25911,6 +26946,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503506</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -26037,6 +27077,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503630</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -26163,6 +27208,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503788</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -26289,6 +27339,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503881</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -26415,6 +27470,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124503939</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -26541,6 +27601,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504184</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -26667,6 +27732,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504203</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -26798,6 +27868,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504371</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -26924,6 +27999,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504472</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -27050,6 +28130,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504533</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -27176,6 +28261,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504560</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -27302,6 +28392,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504630</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -27428,6 +28523,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504665</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -27554,6 +28654,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504729</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -27680,6 +28785,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504787</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -27806,6 +28916,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504889</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -27932,6 +29047,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124504938</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -28058,6 +29178,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124541970</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -28184,6 +29309,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124541985</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -28310,6 +29440,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124541987</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -28436,6 +29571,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542022</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -28562,6 +29702,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542037</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -28688,6 +29833,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542050</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -28814,6 +29964,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542071</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -28940,6 +30095,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542155</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -29066,6 +30226,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542177</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -29192,6 +30357,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542187</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -29323,6 +30493,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542191</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -29449,6 +30624,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542200</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -29570,6 +30750,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124542160</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -29691,6 +30876,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133039898</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -29806,6 +30996,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398767</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -29921,6 +31116,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398768</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -30040,6 +31240,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398769</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -30159,6 +31364,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108276498</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -30278,6 +31488,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398772</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -30403,6 +31618,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122698999</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -30510,6 +31730,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091010</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -30617,6 +31842,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091385</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -30743,6 +31973,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091426</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -30864,6 +32099,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129090983</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -30990,6 +32230,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131577584</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -31108,6 +32353,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54605883</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -31241,6 +32491,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86293398</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -31371,6 +32626,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/721992</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -31513,6 +32773,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598096</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -31631,8 +32896,268 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54597186</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ254"/>
+  <dimension ref="A1:AZ255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22997,10 +22997,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122853226</v>
+        <v>135589649</v>
       </c>
       <c r="B176" t="n">
-        <v>97733</v>
+        <v>57972</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -23008,38 +23008,48 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Hjortronmossen, Lobergs-omr, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>477439</v>
+        <v>475221</v>
       </c>
       <c r="R176" t="n">
-        <v>6593857</v>
+        <v>6593831</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -23066,12 +23076,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -23080,69 +23100,72 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853226</t>
+          <t>https://artportalen.se/Sighting/135589649</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128820267</v>
+        <v>122853226</v>
       </c>
       <c r="B177" t="n">
-        <v>93197</v>
+        <v>97733</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>477509</v>
+        <v>477439</v>
       </c>
       <c r="R177" t="n">
-        <v>6593788</v>
+        <v>6593857</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -23169,22 +23192,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -23193,71 +23206,69 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820267</t>
+          <t>https://artportalen.se/Sighting/122853226</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122853220</v>
+        <v>128820267</v>
       </c>
       <c r="B178" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>477469</v>
+        <v>477509</v>
       </c>
       <c r="R178" t="n">
-        <v>6593854</v>
+        <v>6593788</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -23284,12 +23295,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23298,69 +23319,71 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853220</t>
+          <t>https://artportalen.se/Sighting/128820267</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128295608</v>
+        <v>122853220</v>
       </c>
       <c r="B179" t="n">
-        <v>79413</v>
+        <v>91872</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>477513</v>
+        <v>477469</v>
       </c>
       <c r="R179" t="n">
-        <v>6593853</v>
+        <v>6593854</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -23387,22 +23410,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23411,30 +23424,31 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128295608</t>
+          <t>https://artportalen.se/Sighting/122853220</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128824944</v>
+        <v>128295608</v>
       </c>
       <c r="B180" t="n">
         <v>79413</v>
@@ -23469,10 +23483,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>477452</v>
+        <v>477513</v>
       </c>
       <c r="R180" t="n">
-        <v>6593930</v>
+        <v>6593853</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -23499,22 +23513,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -23540,16 +23554,16 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128824944</t>
+          <t>https://artportalen.se/Sighting/128295608</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128820310</v>
+        <v>128824944</v>
       </c>
       <c r="B181" t="n">
-        <v>57953</v>
+        <v>79413</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -23557,53 +23571,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>477507</v>
+        <v>477452</v>
       </c>
       <c r="R181" t="n">
-        <v>6593779</v>
+        <v>6593930</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -23635,7 +23630,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -23645,12 +23640,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ivrigt födosökande på grangrenar.</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -23676,33 +23666,33 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820310</t>
+          <t>https://artportalen.se/Sighting/128824944</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126223335</v>
+        <v>128820310</v>
       </c>
       <c r="B182" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -23722,7 +23712,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -23732,14 +23722,14 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Övartjärn, Övartjärn, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>475769</v>
+        <v>477507</v>
       </c>
       <c r="R182" t="n">
-        <v>6593275</v>
+        <v>6593779</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -23766,22 +23756,27 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ivrigt födosökande på grangrenar.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -23807,16 +23802,16 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126223335</t>
+          <t>https://artportalen.se/Sighting/128820310</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124776567</v>
+        <v>126223335</v>
       </c>
       <c r="B183" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23824,21 +23819,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -23853,29 +23848,24 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Ostkaktjärn, Vrm</t>
+          <t>Övartjärn, Övartjärn, Vrm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>475615</v>
+        <v>475769</v>
       </c>
       <c r="R183" t="n">
-        <v>6593437</v>
+        <v>6593275</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -23902,12 +23892,22 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -23922,24 +23922,24 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124776567</t>
+          <t>https://artportalen.se/Sighting/126223335</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128956949</v>
+        <v>124776567</v>
       </c>
       <c r="B184" t="n">
         <v>57141</v>
@@ -23974,12 +23974,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -23987,16 +23987,21 @@
           <t>stationär</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Övartjärn, Övartjärn, Vrm</t>
+          <t>Ostkaktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>475772</v>
+        <v>475615</v>
       </c>
       <c r="R184" t="n">
-        <v>6593258</v>
+        <v>6593437</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -24023,27 +24028,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>09:21</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Årstupp.</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -24058,27 +24048,27 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128956949</t>
+          <t>https://artportalen.se/Sighting/124776567</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129457818</v>
+        <v>128956949</v>
       </c>
       <c r="B185" t="n">
-        <v>57132</v>
+        <v>57141</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -24086,53 +24076,53 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
+          <t>Övartjärn, Övartjärn, Vrm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>475574</v>
+        <v>475772</v>
       </c>
       <c r="R185" t="n">
-        <v>6593531</v>
+        <v>6593258</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -24159,22 +24149,27 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Årstupp.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -24200,13 +24195,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129457818</t>
+          <t>https://artportalen.se/Sighting/128956949</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129764125</v>
+        <v>129457818</v>
       </c>
       <c r="B186" t="n">
         <v>57132</v>
@@ -24236,7 +24231,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -24244,6 +24239,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -24251,14 +24251,14 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Övartjärn, Övartjärn, Vrm</t>
+          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>475750</v>
+        <v>475574</v>
       </c>
       <c r="R186" t="n">
-        <v>6593276</v>
+        <v>6593531</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -24285,22 +24285,22 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -24326,16 +24326,16 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129764125</t>
+          <t>https://artportalen.se/Sighting/129457818</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>132741713</v>
+        <v>129764125</v>
       </c>
       <c r="B187" t="n">
-        <v>57165</v>
+        <v>57132</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -24343,16 +24343,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -24362,7 +24362,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -24372,19 +24372,19 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
+          <t>Övartjärn, Övartjärn, Vrm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>475602</v>
+        <v>475750</v>
       </c>
       <c r="R187" t="n">
-        <v>6593448</v>
+        <v>6593276</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -24411,27 +24411,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>4 tuppar,  1 höna.</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -24457,16 +24452,16 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132741713</t>
+          <t>https://artportalen.se/Sighting/129764125</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123246033</v>
+        <v>132741713</v>
       </c>
       <c r="B188" t="n">
-        <v>97733</v>
+        <v>57165</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -24474,38 +24469,48 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2569</v>
+        <v>102613</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>476874</v>
+        <v>475602</v>
       </c>
       <c r="R188" t="n">
-        <v>6592814</v>
+        <v>6593448</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -24532,22 +24537,27 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>4 tuppar,  1 höna.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24556,7 +24566,6 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -24574,51 +24583,55 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123246033</t>
+          <t>https://artportalen.se/Sighting/132741713</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122827482</v>
+        <v>123246033</v>
       </c>
       <c r="B189" t="n">
-        <v>79327</v>
+        <v>97733</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>476811</v>
+        <v>476874</v>
       </c>
       <c r="R189" t="n">
-        <v>6593001</v>
+        <v>6592814</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -24645,22 +24658,22 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24669,6 +24682,7 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -24686,13 +24700,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827482</t>
+          <t>https://artportalen.se/Sighting/123246033</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122827770</v>
+        <v>122827482</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -24727,10 +24741,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>476775</v>
+        <v>476811</v>
       </c>
       <c r="R190" t="n">
-        <v>6593103</v>
+        <v>6593001</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -24762,7 +24776,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24772,7 +24786,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24798,13 +24812,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827770</t>
+          <t>https://artportalen.se/Sighting/122827482</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122853672</v>
+        <v>122827770</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -24833,19 +24847,16 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>476703</v>
+        <v>476775</v>
       </c>
       <c r="R191" t="n">
-        <v>6593133</v>
+        <v>6593103</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -24872,12 +24883,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24886,31 +24907,30 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853672</t>
+          <t>https://artportalen.se/Sighting/122827770</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122853678</v>
+        <v>122853672</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -24948,10 +24968,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>476700</v>
+        <v>476703</v>
       </c>
       <c r="R192" t="n">
-        <v>6593134</v>
+        <v>6593133</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -25010,38 +25030,38 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853678</t>
+          <t>https://artportalen.se/Sighting/122853672</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122853683</v>
+        <v>122853678</v>
       </c>
       <c r="B193" t="n">
-        <v>75428</v>
+        <v>79327</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -25054,10 +25074,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>476692</v>
+        <v>476700</v>
       </c>
       <c r="R193" t="n">
-        <v>6593147</v>
+        <v>6593134</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -25116,16 +25136,16 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853683</t>
+          <t>https://artportalen.se/Sighting/122853678</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122826361</v>
+        <v>122853683</v>
       </c>
       <c r="B194" t="n">
-        <v>79084</v>
+        <v>75428</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -25133,34 +25153,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>476870</v>
+        <v>476692</v>
       </c>
       <c r="R194" t="n">
-        <v>6593000</v>
+        <v>6593147</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -25187,22 +25210,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25211,33 +25224,34 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122826361</t>
+          <t>https://artportalen.se/Sighting/122853683</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122827273</v>
+        <v>122826361</v>
       </c>
       <c r="B195" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -25245,21 +25259,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -25269,10 +25283,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>476842</v>
+        <v>476870</v>
       </c>
       <c r="R195" t="n">
-        <v>6592963</v>
+        <v>6593000</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -25304,7 +25318,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -25314,7 +25328,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25340,13 +25354,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827273</t>
+          <t>https://artportalen.se/Sighting/122826361</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122827376</v>
+        <v>122827273</v>
       </c>
       <c r="B196" t="n">
         <v>79946</v>
@@ -25381,10 +25395,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>476815</v>
+        <v>476842</v>
       </c>
       <c r="R196" t="n">
-        <v>6593013</v>
+        <v>6592963</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -25416,7 +25430,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -25426,7 +25440,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25452,16 +25466,16 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827376</t>
+          <t>https://artportalen.se/Sighting/122827273</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122826109</v>
+        <v>122827376</v>
       </c>
       <c r="B197" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -25469,21 +25483,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -25493,10 +25507,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>476865</v>
+        <v>476815</v>
       </c>
       <c r="R197" t="n">
-        <v>6592990</v>
+        <v>6593013</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -25528,7 +25542,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -25538,7 +25552,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25564,16 +25578,16 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122826109</t>
+          <t>https://artportalen.se/Sighting/122827376</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122828141</v>
+        <v>122826109</v>
       </c>
       <c r="B198" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -25581,21 +25595,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -25605,10 +25619,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>476735</v>
+        <v>476865</v>
       </c>
       <c r="R198" t="n">
-        <v>6593133</v>
+        <v>6592990</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -25640,7 +25654,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -25650,7 +25664,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25676,51 +25690,51 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122828141</t>
+          <t>https://artportalen.se/Sighting/122826109</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124505050</v>
+        <v>122828141</v>
       </c>
       <c r="B199" t="n">
-        <v>79327</v>
+        <v>79917</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>482221</v>
+        <v>476735</v>
       </c>
       <c r="R199" t="n">
-        <v>6590913</v>
+        <v>6593133</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -25747,22 +25761,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25788,13 +25802,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124505050</t>
+          <t>https://artportalen.se/Sighting/122828141</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124505147</v>
+        <v>124505050</v>
       </c>
       <c r="B200" t="n">
         <v>79327</v>
@@ -25829,10 +25843,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>482216</v>
+        <v>482221</v>
       </c>
       <c r="R200" t="n">
-        <v>6590937</v>
+        <v>6590913</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -25864,7 +25878,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -25874,7 +25888,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25900,70 +25914,51 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124505147</t>
+          <t>https://artportalen.se/Sighting/124505050</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124502716</v>
+        <v>124505147</v>
       </c>
       <c r="B201" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>482257</v>
+        <v>482216</v>
       </c>
       <c r="R201" t="n">
-        <v>6590830</v>
+        <v>6590937</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -25995,7 +25990,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -26005,7 +26000,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -26031,13 +26026,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502716</t>
+          <t>https://artportalen.se/Sighting/124505147</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124502759</v>
+        <v>124502716</v>
       </c>
       <c r="B202" t="n">
         <v>57141</v>
@@ -26091,10 +26086,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>482259</v>
+        <v>482257</v>
       </c>
       <c r="R202" t="n">
-        <v>6590829</v>
+        <v>6590830</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -26126,7 +26121,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -26136,7 +26131,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26162,13 +26157,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502759</t>
+          <t>https://artportalen.se/Sighting/124502716</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124502785</v>
+        <v>124502759</v>
       </c>
       <c r="B203" t="n">
         <v>57141</v>
@@ -26222,10 +26217,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>482273</v>
+        <v>482259</v>
       </c>
       <c r="R203" t="n">
-        <v>6590828</v>
+        <v>6590829</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -26257,7 +26252,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -26267,7 +26262,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -26293,13 +26288,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502785</t>
+          <t>https://artportalen.se/Sighting/124502759</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124502909</v>
+        <v>124502785</v>
       </c>
       <c r="B204" t="n">
         <v>57141</v>
@@ -26349,14 +26344,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
+          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>482286</v>
+        <v>482273</v>
       </c>
       <c r="R204" t="n">
-        <v>6590831</v>
+        <v>6590828</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -26388,7 +26383,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -26398,7 +26393,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -26424,13 +26419,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502909</t>
+          <t>https://artportalen.se/Sighting/124502785</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124503058</v>
+        <v>124502909</v>
       </c>
       <c r="B205" t="n">
         <v>57141</v>
@@ -26484,10 +26479,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>482329</v>
+        <v>482286</v>
       </c>
       <c r="R205" t="n">
-        <v>6590870</v>
+        <v>6590831</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -26519,7 +26514,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -26529,7 +26524,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26555,13 +26550,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503058</t>
+          <t>https://artportalen.se/Sighting/124502909</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124503101</v>
+        <v>124503058</v>
       </c>
       <c r="B206" t="n">
         <v>57141</v>
@@ -26606,7 +26601,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -26615,10 +26610,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>482328</v>
+        <v>482329</v>
       </c>
       <c r="R206" t="n">
-        <v>6590871</v>
+        <v>6590870</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -26650,7 +26645,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -26660,7 +26655,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26686,13 +26681,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503101</t>
+          <t>https://artportalen.se/Sighting/124503058</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124503372</v>
+        <v>124503101</v>
       </c>
       <c r="B207" t="n">
         <v>57141</v>
@@ -26737,7 +26732,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -26746,10 +26741,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>482345</v>
+        <v>482328</v>
       </c>
       <c r="R207" t="n">
-        <v>6590890</v>
+        <v>6590871</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -26781,7 +26776,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -26791,7 +26786,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26817,13 +26812,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503372</t>
+          <t>https://artportalen.se/Sighting/124503101</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124503506</v>
+        <v>124503372</v>
       </c>
       <c r="B208" t="n">
         <v>57141</v>
@@ -26877,10 +26872,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>482356</v>
+        <v>482345</v>
       </c>
       <c r="R208" t="n">
-        <v>6590902</v>
+        <v>6590890</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -26912,7 +26907,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -26922,7 +26917,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -26948,13 +26943,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503506</t>
+          <t>https://artportalen.se/Sighting/124503372</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124503630</v>
+        <v>124503506</v>
       </c>
       <c r="B209" t="n">
         <v>57141</v>
@@ -27008,10 +27003,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>482376</v>
+        <v>482356</v>
       </c>
       <c r="R209" t="n">
-        <v>6590925</v>
+        <v>6590902</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -27043,7 +27038,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -27053,7 +27048,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27079,13 +27074,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503630</t>
+          <t>https://artportalen.se/Sighting/124503506</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124503788</v>
+        <v>124503630</v>
       </c>
       <c r="B210" t="n">
         <v>57141</v>
@@ -27139,10 +27134,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>482320</v>
+        <v>482376</v>
       </c>
       <c r="R210" t="n">
-        <v>6590989</v>
+        <v>6590925</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -27174,7 +27169,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -27184,7 +27179,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27210,13 +27205,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503788</t>
+          <t>https://artportalen.se/Sighting/124503630</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124503881</v>
+        <v>124503788</v>
       </c>
       <c r="B211" t="n">
         <v>57141</v>
@@ -27270,10 +27265,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>482318</v>
+        <v>482320</v>
       </c>
       <c r="R211" t="n">
-        <v>6590992</v>
+        <v>6590989</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -27305,7 +27300,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -27315,7 +27310,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -27341,13 +27336,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503881</t>
+          <t>https://artportalen.se/Sighting/124503788</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124503939</v>
+        <v>124503881</v>
       </c>
       <c r="B212" t="n">
         <v>57141</v>
@@ -27401,10 +27396,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>482283</v>
+        <v>482318</v>
       </c>
       <c r="R212" t="n">
-        <v>6591027</v>
+        <v>6590992</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -27436,7 +27431,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -27446,7 +27441,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -27472,13 +27467,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503939</t>
+          <t>https://artportalen.se/Sighting/124503881</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124504184</v>
+        <v>124503939</v>
       </c>
       <c r="B213" t="n">
         <v>57141</v>
@@ -27523,7 +27518,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -27532,10 +27527,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>482319</v>
+        <v>482283</v>
       </c>
       <c r="R213" t="n">
-        <v>6590941</v>
+        <v>6591027</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -27567,7 +27562,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -27577,7 +27572,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -27603,13 +27598,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504184</t>
+          <t>https://artportalen.se/Sighting/124503939</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124504203</v>
+        <v>124504184</v>
       </c>
       <c r="B214" t="n">
         <v>57141</v>
@@ -27654,7 +27649,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -27663,10 +27658,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>482320</v>
+        <v>482319</v>
       </c>
       <c r="R214" t="n">
-        <v>6590940</v>
+        <v>6590941</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -27734,13 +27729,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504203</t>
+          <t>https://artportalen.se/Sighting/124504184</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124504371</v>
+        <v>124504203</v>
       </c>
       <c r="B215" t="n">
         <v>57141</v>
@@ -27797,7 +27792,7 @@
         <v>482320</v>
       </c>
       <c r="R215" t="n">
-        <v>6590938</v>
+        <v>6590940</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -27829,7 +27824,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -27839,12 +27834,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -27870,13 +27860,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504371</t>
+          <t>https://artportalen.se/Sighting/124504203</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124504472</v>
+        <v>124504371</v>
       </c>
       <c r="B216" t="n">
         <v>57141</v>
@@ -27930,10 +27920,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>482306</v>
+        <v>482320</v>
       </c>
       <c r="R216" t="n">
-        <v>6590920</v>
+        <v>6590938</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -27965,7 +27955,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -27975,7 +27965,12 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28001,13 +27996,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504472</t>
+          <t>https://artportalen.se/Sighting/124504371</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124504533</v>
+        <v>124504472</v>
       </c>
       <c r="B217" t="n">
         <v>57141</v>
@@ -28061,10 +28056,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>482316</v>
+        <v>482306</v>
       </c>
       <c r="R217" t="n">
-        <v>6590915</v>
+        <v>6590920</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -28096,7 +28091,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -28106,7 +28101,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28132,13 +28127,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504533</t>
+          <t>https://artportalen.se/Sighting/124504472</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124504560</v>
+        <v>124504533</v>
       </c>
       <c r="B218" t="n">
         <v>57141</v>
@@ -28192,10 +28187,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>482303</v>
+        <v>482316</v>
       </c>
       <c r="R218" t="n">
-        <v>6590900</v>
+        <v>6590915</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -28227,7 +28222,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -28237,7 +28232,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -28263,13 +28258,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504560</t>
+          <t>https://artportalen.se/Sighting/124504533</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124504630</v>
+        <v>124504560</v>
       </c>
       <c r="B219" t="n">
         <v>57141</v>
@@ -28314,7 +28309,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -28323,10 +28318,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>482305</v>
+        <v>482303</v>
       </c>
       <c r="R219" t="n">
-        <v>6590892</v>
+        <v>6590900</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -28358,7 +28353,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -28368,7 +28363,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -28394,13 +28389,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504630</t>
+          <t>https://artportalen.se/Sighting/124504560</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124504665</v>
+        <v>124504630</v>
       </c>
       <c r="B220" t="n">
         <v>57141</v>
@@ -28445,7 +28440,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -28454,10 +28449,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>482301</v>
+        <v>482305</v>
       </c>
       <c r="R220" t="n">
-        <v>6590884</v>
+        <v>6590892</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -28489,7 +28484,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -28499,7 +28494,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -28525,13 +28520,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504665</t>
+          <t>https://artportalen.se/Sighting/124504630</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124504729</v>
+        <v>124504665</v>
       </c>
       <c r="B221" t="n">
         <v>57141</v>
@@ -28585,10 +28580,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>482279</v>
+        <v>482301</v>
       </c>
       <c r="R221" t="n">
-        <v>6590867</v>
+        <v>6590884</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -28620,7 +28615,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -28630,7 +28625,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -28656,13 +28651,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504729</t>
+          <t>https://artportalen.se/Sighting/124504665</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124504787</v>
+        <v>124504729</v>
       </c>
       <c r="B222" t="n">
         <v>57141</v>
@@ -28716,10 +28711,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>482260</v>
+        <v>482279</v>
       </c>
       <c r="R222" t="n">
-        <v>6590864</v>
+        <v>6590867</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -28751,7 +28746,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -28761,7 +28756,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -28787,13 +28782,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504787</t>
+          <t>https://artportalen.se/Sighting/124504729</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124504889</v>
+        <v>124504787</v>
       </c>
       <c r="B223" t="n">
         <v>57141</v>
@@ -28843,14 +28838,14 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
+          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>482243</v>
+        <v>482260</v>
       </c>
       <c r="R223" t="n">
-        <v>6590887</v>
+        <v>6590864</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -28882,7 +28877,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -28892,7 +28887,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -28918,13 +28913,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504889</t>
+          <t>https://artportalen.se/Sighting/124504787</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124504938</v>
+        <v>124504889</v>
       </c>
       <c r="B224" t="n">
         <v>57141</v>
@@ -28978,10 +28973,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>482242</v>
+        <v>482243</v>
       </c>
       <c r="R224" t="n">
-        <v>6590889</v>
+        <v>6590887</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -29013,7 +29008,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -29023,7 +29018,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -29049,13 +29044,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504938</t>
+          <t>https://artportalen.se/Sighting/124504889</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124541970</v>
+        <v>124504938</v>
       </c>
       <c r="B225" t="n">
         <v>57141</v>
@@ -29105,14 +29100,14 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
+          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>482334</v>
+        <v>482242</v>
       </c>
       <c r="R225" t="n">
-        <v>6590967</v>
+        <v>6590889</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -29139,22 +29134,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -29180,13 +29175,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124541970</t>
+          <t>https://artportalen.se/Sighting/124504938</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124541985</v>
+        <v>124541970</v>
       </c>
       <c r="B226" t="n">
         <v>57141</v>
@@ -29236,14 +29231,14 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
+          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>482253</v>
+        <v>482334</v>
       </c>
       <c r="R226" t="n">
-        <v>6590827</v>
+        <v>6590967</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -29275,7 +29270,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -29285,7 +29280,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -29311,13 +29306,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124541985</t>
+          <t>https://artportalen.se/Sighting/124541970</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124541987</v>
+        <v>124541985</v>
       </c>
       <c r="B227" t="n">
         <v>57141</v>
@@ -29371,10 +29366,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>482262</v>
+        <v>482253</v>
       </c>
       <c r="R227" t="n">
-        <v>6590843</v>
+        <v>6590827</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -29406,7 +29401,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -29416,7 +29411,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -29442,13 +29437,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124541987</t>
+          <t>https://artportalen.se/Sighting/124541985</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124542022</v>
+        <v>124541987</v>
       </c>
       <c r="B228" t="n">
         <v>57141</v>
@@ -29498,14 +29493,14 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
+          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>482299</v>
+        <v>482262</v>
       </c>
       <c r="R228" t="n">
-        <v>6590938</v>
+        <v>6590843</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -29537,7 +29532,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -29547,7 +29542,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -29573,13 +29568,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542022</t>
+          <t>https://artportalen.se/Sighting/124541987</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124542037</v>
+        <v>124542022</v>
       </c>
       <c r="B229" t="n">
         <v>57141</v>
@@ -29624,7 +29619,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -29633,10 +29628,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>482327</v>
+        <v>482299</v>
       </c>
       <c r="R229" t="n">
-        <v>6590995</v>
+        <v>6590938</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -29668,7 +29663,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -29678,7 +29673,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -29704,13 +29699,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542037</t>
+          <t>https://artportalen.se/Sighting/124542022</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124542050</v>
+        <v>124542037</v>
       </c>
       <c r="B230" t="n">
         <v>57141</v>
@@ -29755,7 +29750,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -29764,10 +29759,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>482353</v>
+        <v>482327</v>
       </c>
       <c r="R230" t="n">
-        <v>6591028</v>
+        <v>6590995</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -29799,7 +29794,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -29809,7 +29804,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -29835,13 +29830,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542050</t>
+          <t>https://artportalen.se/Sighting/124542037</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124542071</v>
+        <v>124542050</v>
       </c>
       <c r="B231" t="n">
         <v>57141</v>
@@ -29895,10 +29890,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>482383</v>
+        <v>482353</v>
       </c>
       <c r="R231" t="n">
-        <v>6591056</v>
+        <v>6591028</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -29930,7 +29925,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -29940,7 +29935,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -29966,13 +29961,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542071</t>
+          <t>https://artportalen.se/Sighting/124542050</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124542155</v>
+        <v>124542071</v>
       </c>
       <c r="B232" t="n">
         <v>57141</v>
@@ -30026,10 +30021,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>482307</v>
+        <v>482383</v>
       </c>
       <c r="R232" t="n">
-        <v>6591054</v>
+        <v>6591056</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -30061,7 +30056,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -30071,7 +30066,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -30097,13 +30092,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542155</t>
+          <t>https://artportalen.se/Sighting/124542071</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124542177</v>
+        <v>124542155</v>
       </c>
       <c r="B233" t="n">
         <v>57141</v>
@@ -30157,10 +30152,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>482296</v>
+        <v>482307</v>
       </c>
       <c r="R233" t="n">
-        <v>6591064</v>
+        <v>6591054</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -30192,7 +30187,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>06:16</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -30202,7 +30197,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>06:16</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -30228,13 +30223,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542177</t>
+          <t>https://artportalen.se/Sighting/124542155</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124542187</v>
+        <v>124542177</v>
       </c>
       <c r="B234" t="n">
         <v>57141</v>
@@ -30279,7 +30274,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -30288,10 +30283,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>482254</v>
+        <v>482296</v>
       </c>
       <c r="R234" t="n">
-        <v>6591068</v>
+        <v>6591064</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -30323,7 +30318,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -30333,7 +30328,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -30359,13 +30354,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542187</t>
+          <t>https://artportalen.se/Sighting/124542177</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124542191</v>
+        <v>124542187</v>
       </c>
       <c r="B235" t="n">
         <v>57141</v>
@@ -30410,7 +30405,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -30419,10 +30414,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>482255</v>
+        <v>482254</v>
       </c>
       <c r="R235" t="n">
-        <v>6591067</v>
+        <v>6591068</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -30454,7 +30449,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -30464,12 +30459,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>06:19</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -30495,13 +30485,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542191</t>
+          <t>https://artportalen.se/Sighting/124542187</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124542200</v>
+        <v>124542191</v>
       </c>
       <c r="B236" t="n">
         <v>57141</v>
@@ -30555,10 +30545,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>482293</v>
+        <v>482255</v>
       </c>
       <c r="R236" t="n">
-        <v>6591125</v>
+        <v>6591067</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -30590,7 +30580,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -30600,7 +30590,12 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -30626,38 +30621,38 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542200</t>
+          <t>https://artportalen.se/Sighting/124542191</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124542160</v>
+        <v>124542200</v>
       </c>
       <c r="B237" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -30670,9 +30665,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -30681,10 +30681,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>482222</v>
+        <v>482293</v>
       </c>
       <c r="R237" t="n">
-        <v>6590970</v>
+        <v>6591125</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -30716,7 +30716,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -30752,16 +30752,16 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542160</t>
+          <t>https://artportalen.se/Sighting/124542200</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>133039898</v>
+        <v>124542160</v>
       </c>
       <c r="B238" t="n">
-        <v>57391</v>
+        <v>58114</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -30769,21 +30769,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>102961</v>
+        <v>103021</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -30803,14 +30803,14 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Fisklösen norr, Fisklösen norr, Vrm</t>
+          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>480277</v>
+        <v>482222</v>
       </c>
       <c r="R238" t="n">
-        <v>6590888</v>
+        <v>6590970</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -30837,22 +30837,22 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>04:32</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>04:32</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30878,38 +30878,38 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133039898</t>
+          <t>https://artportalen.se/Sighting/124542160</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>132398767</v>
+        <v>133039898</v>
       </c>
       <c r="B239" t="n">
-        <v>57280</v>
+        <v>57391</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100065</v>
+        <v>102961</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -30917,23 +30917,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Bastkulltjärnen, Vrm</t>
+          <t>Fisklösen norr, Fisklösen norr, Vrm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>480848</v>
+        <v>480277</v>
       </c>
       <c r="R239" t="n">
-        <v>6588847</v>
+        <v>6590888</v>
       </c>
       <c r="S239" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -30957,22 +30963,22 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>04:32</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>04:32</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30987,49 +30993,49 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398767</t>
+          <t>https://artportalen.se/Sighting/133039898</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>132398768</v>
+        <v>132398767</v>
       </c>
       <c r="B240" t="n">
-        <v>57585</v>
+        <v>57280</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>102966</v>
+        <v>100065</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -31118,38 +31124,38 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398768</t>
+          <t>https://artportalen.se/Sighting/132398767</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>132398769</v>
+        <v>132398768</v>
       </c>
       <c r="B241" t="n">
-        <v>57969</v>
+        <v>57585</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>102977</v>
+        <v>102966</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -31159,11 +31165,7 @@
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
@@ -31242,33 +31244,33 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398769</t>
+          <t>https://artportalen.se/Sighting/132398768</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>108276498</v>
+        <v>132398769</v>
       </c>
       <c r="B242" t="n">
-        <v>58541</v>
+        <v>57969</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>102987</v>
+        <v>102977</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -31285,23 +31287,23 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
+          <t>Bastkulltjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>480700</v>
+        <v>480848</v>
       </c>
       <c r="R242" t="n">
-        <v>6588844</v>
+        <v>6588847</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -31325,22 +31327,22 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -31355,27 +31357,27 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108276498</t>
+          <t>https://artportalen.se/Sighting/132398769</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>132398772</v>
+        <v>108276498</v>
       </c>
       <c r="B243" t="n">
-        <v>58136</v>
+        <v>58541</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -31383,21 +31385,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103021</v>
+        <v>102987</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -31409,23 +31411,23 @@
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Bastkulltjärnen, Vrm</t>
+          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>480848</v>
+        <v>480700</v>
       </c>
       <c r="R243" t="n">
-        <v>6588847</v>
+        <v>6588844</v>
       </c>
       <c r="S243" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -31449,22 +31451,22 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -31479,82 +31481,77 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398772</t>
+          <t>https://artportalen.se/Sighting/108276498</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122698999</v>
+        <v>132398772</v>
       </c>
       <c r="B244" t="n">
-        <v>58790</v>
+        <v>58136</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>ex.</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>dvala</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
+          <t>Bastkulltjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>480766</v>
+        <v>480848</v>
       </c>
       <c r="R244" t="n">
-        <v>6588916</v>
+        <v>6588847</v>
       </c>
       <c r="S244" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -31578,22 +31575,22 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -31602,34 +31599,33 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122698999</t>
+          <t>https://artportalen.se/Sighting/132398772</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129091010</v>
+        <v>122698999</v>
       </c>
       <c r="B245" t="n">
-        <v>91872</v>
+        <v>58790</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -31637,37 +31633,54 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5447</v>
+        <v>208245</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>dvala</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Bastkulltjärnen, Bastkulltjärnen, Vrm</t>
+          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>481291</v>
+        <v>480766</v>
       </c>
       <c r="R245" t="n">
-        <v>6589086</v>
+        <v>6588916</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -31691,22 +31704,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -31715,55 +31728,56 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129091010</t>
+          <t>https://artportalen.se/Sighting/122698999</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129091385</v>
+        <v>129091010</v>
       </c>
       <c r="B246" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -31773,10 +31787,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>481127</v>
+        <v>481291</v>
       </c>
       <c r="R246" t="n">
-        <v>6589109</v>
+        <v>6589086</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -31808,7 +31822,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -31818,7 +31832,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -31844,65 +31858,51 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129091385</t>
+          <t>https://artportalen.se/Sighting/129091010</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129091426</v>
+        <v>129091385</v>
       </c>
       <c r="B247" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
+          <t>Bastkulltjärnen, Bastkulltjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q247" t="n">
         <v>481127</v>
       </c>
       <c r="R247" t="n">
-        <v>6589108</v>
+        <v>6589109</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -31934,7 +31934,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -31944,12 +31944,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -31975,16 +31970,16 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129091426</t>
+          <t>https://artportalen.se/Sighting/129091385</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129090983</v>
+        <v>129091426</v>
       </c>
       <c r="B248" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31992,21 +31987,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -32030,10 +32025,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>481289</v>
+        <v>481127</v>
       </c>
       <c r="R248" t="n">
-        <v>6589051</v>
+        <v>6589108</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -32065,7 +32060,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -32075,7 +32070,12 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -32101,16 +32101,16 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090983</t>
+          <t>https://artportalen.se/Sighting/129091426</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131577584</v>
+        <v>129090983</v>
       </c>
       <c r="B249" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -32118,21 +32118,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -32147,19 +32147,19 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Stenbotjärnsbäcken, Stenbotjärnsbäcken, Vrm</t>
+          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>480931</v>
+        <v>481289</v>
       </c>
       <c r="R249" t="n">
-        <v>6587529</v>
+        <v>6589051</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -32186,27 +32186,22 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Rejält ringbarkad tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -32232,65 +32227,68 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131577584</t>
+          <t>https://artportalen.se/Sighting/129090983</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>54605883</v>
+        <v>131577584</v>
       </c>
       <c r="B250" t="n">
-        <v>96313</v>
+        <v>57975</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>530</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Kärmen, Nrk</t>
+          <t>Stenbotjärnsbäcken, Stenbotjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>485029</v>
+        <v>480931</v>
       </c>
       <c r="R250" t="n">
-        <v>6574808</v>
+        <v>6587529</v>
       </c>
       <c r="S250" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -32304,7 +32302,7 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
@@ -32314,12 +32312,27 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Rejält ringbarkad tall.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -32330,95 +32343,80 @@
       </c>
       <c r="AG250" t="b">
         <v>0</v>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>sten i skyddat läge ganska nära dämmet</t>
-        </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54605883</t>
+          <t>https://artportalen.se/Sighting/131577584</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>86293398</v>
+        <v>54605883</v>
       </c>
       <c r="B251" t="n">
-        <v>110078</v>
+        <v>96313</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>220299</v>
+        <v>530</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Norviken, V om, Nrk</t>
+          <t>Kärmen, Nrk</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>483641</v>
+        <v>485029</v>
       </c>
       <c r="R251" t="n">
-        <v>6573880</v>
+        <v>6574808</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -32440,24 +32438,14 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Kar-0070</t>
-        </is>
-      </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -32466,70 +32454,70 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
-      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>sten i skyddat läge ganska nära dämmet</t>
         </is>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY251" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86293398</t>
+          <t>https://artportalen.se/Sighting/54605883</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>721992</v>
+        <v>86293398</v>
       </c>
       <c r="B252" t="n">
-        <v>104211</v>
+        <v>110078</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1910</v>
+        <v>220299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -32542,16 +32530,18 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Blomsterhult, 450 m NO om, Nrk</t>
+          <t>Norviken, V om, Nrk</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>486559</v>
+        <v>483641</v>
       </c>
       <c r="R252" t="n">
-        <v>6572552</v>
+        <v>6573880</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -32578,22 +32568,22 @@
       </c>
       <c r="X252" t="inlineStr">
         <is>
-          <t>T-Kar-0152</t>
+          <t>Arkiv-T-Kar-0070</t>
         </is>
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Upptäckt 2009.</t>
+          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -32602,12 +32592,13 @@
       <c r="AE252" t="b">
         <v>0</v>
       </c>
+      <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="b">
         <v>0</v>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
+          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
         </is>
       </c>
       <c r="AT252" t="inlineStr"/>
@@ -32623,64 +32614,73 @@
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/721992</t>
+          <t>https://artportalen.se/Sighting/86293398</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>125598096</v>
+        <v>721992</v>
       </c>
       <c r="B253" t="n">
-        <v>57950</v>
+        <v>104211</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100049</v>
+        <v>1910</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Kärmsön, Kärmsön, Nrk</t>
+          <t>Blomsterhult, 450 m NO om, Nrk</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>485667</v>
+        <v>486559</v>
       </c>
       <c r="R253" t="n">
-        <v>6572353</v>
+        <v>6572552</v>
       </c>
       <c r="S253" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -32702,29 +32702,24 @@
           <t>Karlskoga</t>
         </is>
       </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>T-Kar-0152</t>
+        </is>
+      </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2009-07-28</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2009-07-28</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Färska hack i högstubbe</t>
+          <t>Upptäckt 2009.</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -32736,55 +32731,39 @@
       <c r="AG253" t="b">
         <v>0</v>
       </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
-        </is>
-      </c>
-      <c r="AY253" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125598096</t>
+          <t>https://artportalen.se/Sighting/721992</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>54597186</v>
+        <v>125598096</v>
       </c>
       <c r="B254" t="n">
-        <v>96313</v>
+        <v>57950</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32792,48 +32771,42 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>530</v>
+        <v>100049</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>L Noren, Nrk</t>
+          <t>Kärmsön, Kärmsön, Nrk</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>484632</v>
+        <v>485667</v>
       </c>
       <c r="R254" t="n">
-        <v>6571731</v>
+        <v>6572353</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -32857,12 +32830,27 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Färska hack i högstubbe</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -32874,29 +32862,167 @@
       <c r="AG254" t="b">
         <v>0</v>
       </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598096</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>54597186</v>
+      </c>
+      <c r="B255" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>530</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>L Noren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>484632</v>
+      </c>
+      <c r="R255" t="n">
+        <v>6571731</v>
+      </c>
+      <c r="S255" t="n">
+        <v>10</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54597186</t>
         </is>
@@ -33157,6 +33283,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -23000,7 +23000,7 @@
         <v>135589649</v>
       </c>
       <c r="B176" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ254"/>
+  <dimension ref="A1:AZ255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22997,10 +22997,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122853226</v>
+        <v>135589649</v>
       </c>
       <c r="B176" t="n">
-        <v>97733</v>
+        <v>57977</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -23008,38 +23008,48 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Hjortronmossen, Lobergs-omr, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>477439</v>
+        <v>475221</v>
       </c>
       <c r="R176" t="n">
-        <v>6593857</v>
+        <v>6593831</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -23066,12 +23076,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -23080,69 +23100,72 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853226</t>
+          <t>https://artportalen.se/Sighting/135589649</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128820267</v>
+        <v>122853226</v>
       </c>
       <c r="B177" t="n">
-        <v>93197</v>
+        <v>97733</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>477509</v>
+        <v>477439</v>
       </c>
       <c r="R177" t="n">
-        <v>6593788</v>
+        <v>6593857</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -23169,22 +23192,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -23193,71 +23206,69 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820267</t>
+          <t>https://artportalen.se/Sighting/122853226</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122853220</v>
+        <v>128820267</v>
       </c>
       <c r="B178" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>477469</v>
+        <v>477509</v>
       </c>
       <c r="R178" t="n">
-        <v>6593854</v>
+        <v>6593788</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -23284,12 +23295,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23298,69 +23319,71 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853220</t>
+          <t>https://artportalen.se/Sighting/128820267</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128295608</v>
+        <v>122853220</v>
       </c>
       <c r="B179" t="n">
-        <v>79413</v>
+        <v>91872</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>477513</v>
+        <v>477469</v>
       </c>
       <c r="R179" t="n">
-        <v>6593853</v>
+        <v>6593854</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -23387,22 +23410,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23411,30 +23424,31 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128295608</t>
+          <t>https://artportalen.se/Sighting/122853220</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128824944</v>
+        <v>128295608</v>
       </c>
       <c r="B180" t="n">
         <v>79413</v>
@@ -23469,10 +23483,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>477452</v>
+        <v>477513</v>
       </c>
       <c r="R180" t="n">
-        <v>6593930</v>
+        <v>6593853</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -23499,22 +23513,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -23540,16 +23554,16 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128824944</t>
+          <t>https://artportalen.se/Sighting/128295608</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128820310</v>
+        <v>128824944</v>
       </c>
       <c r="B181" t="n">
-        <v>57953</v>
+        <v>79413</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -23557,53 +23571,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>477507</v>
+        <v>477452</v>
       </c>
       <c r="R181" t="n">
-        <v>6593779</v>
+        <v>6593930</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -23635,7 +23630,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -23645,12 +23640,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ivrigt födosökande på grangrenar.</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -23676,33 +23666,33 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820310</t>
+          <t>https://artportalen.se/Sighting/128824944</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126223335</v>
+        <v>128820310</v>
       </c>
       <c r="B182" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -23722,7 +23712,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -23732,14 +23722,14 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Övartjärn, Övartjärn, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>475769</v>
+        <v>477507</v>
       </c>
       <c r="R182" t="n">
-        <v>6593275</v>
+        <v>6593779</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -23766,22 +23756,27 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ivrigt födosökande på grangrenar.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -23807,16 +23802,16 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126223335</t>
+          <t>https://artportalen.se/Sighting/128820310</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124776567</v>
+        <v>126223335</v>
       </c>
       <c r="B183" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23824,21 +23819,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -23853,29 +23848,24 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Ostkaktjärn, Vrm</t>
+          <t>Övartjärn, Övartjärn, Vrm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>475615</v>
+        <v>475769</v>
       </c>
       <c r="R183" t="n">
-        <v>6593437</v>
+        <v>6593275</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -23902,12 +23892,22 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -23922,24 +23922,24 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124776567</t>
+          <t>https://artportalen.se/Sighting/126223335</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128956949</v>
+        <v>124776567</v>
       </c>
       <c r="B184" t="n">
         <v>57141</v>
@@ -23974,12 +23974,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -23987,16 +23987,21 @@
           <t>stationär</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Övartjärn, Övartjärn, Vrm</t>
+          <t>Ostkaktjärn, Vrm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>475772</v>
+        <v>475615</v>
       </c>
       <c r="R184" t="n">
-        <v>6593258</v>
+        <v>6593437</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -24023,27 +24028,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>09:21</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Årstupp.</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -24058,27 +24048,27 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128956949</t>
+          <t>https://artportalen.se/Sighting/124776567</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129457818</v>
+        <v>128956949</v>
       </c>
       <c r="B185" t="n">
-        <v>57132</v>
+        <v>57141</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -24086,53 +24076,53 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
+          <t>Övartjärn, Övartjärn, Vrm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>475574</v>
+        <v>475772</v>
       </c>
       <c r="R185" t="n">
-        <v>6593531</v>
+        <v>6593258</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -24159,22 +24149,27 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Årstupp.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -24200,13 +24195,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129457818</t>
+          <t>https://artportalen.se/Sighting/128956949</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129764125</v>
+        <v>129457818</v>
       </c>
       <c r="B186" t="n">
         <v>57132</v>
@@ -24236,7 +24231,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -24244,6 +24239,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -24251,14 +24251,14 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Övartjärn, Övartjärn, Vrm</t>
+          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>475750</v>
+        <v>475574</v>
       </c>
       <c r="R186" t="n">
-        <v>6593276</v>
+        <v>6593531</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -24285,22 +24285,22 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -24326,16 +24326,16 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129764125</t>
+          <t>https://artportalen.se/Sighting/129457818</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>132741713</v>
+        <v>129764125</v>
       </c>
       <c r="B187" t="n">
-        <v>57165</v>
+        <v>57132</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -24343,16 +24343,16 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -24362,7 +24362,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -24372,19 +24372,19 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
+          <t>Övartjärn, Övartjärn, Vrm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>475602</v>
+        <v>475750</v>
       </c>
       <c r="R187" t="n">
-        <v>6593448</v>
+        <v>6593276</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -24411,27 +24411,22 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>4 tuppar,  1 höna.</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -24457,16 +24452,16 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132741713</t>
+          <t>https://artportalen.se/Sighting/129764125</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123246033</v>
+        <v>132741713</v>
       </c>
       <c r="B188" t="n">
-        <v>97733</v>
+        <v>57165</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -24474,38 +24469,48 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2569</v>
+        <v>102613</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Ostkaktjärn, Lobergs-omr, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>476874</v>
+        <v>475602</v>
       </c>
       <c r="R188" t="n">
-        <v>6592814</v>
+        <v>6593448</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -24532,22 +24537,27 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>4 tuppar,  1 höna.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24556,7 +24566,6 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -24574,51 +24583,55 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123246033</t>
+          <t>https://artportalen.se/Sighting/132741713</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>122827482</v>
+        <v>123246033</v>
       </c>
       <c r="B189" t="n">
-        <v>79327</v>
+        <v>97733</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>476811</v>
+        <v>476874</v>
       </c>
       <c r="R189" t="n">
-        <v>6593001</v>
+        <v>6592814</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -24645,22 +24658,22 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24669,6 +24682,7 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -24686,13 +24700,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827482</t>
+          <t>https://artportalen.se/Sighting/123246033</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>122827770</v>
+        <v>122827482</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -24727,10 +24741,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>476775</v>
+        <v>476811</v>
       </c>
       <c r="R190" t="n">
-        <v>6593103</v>
+        <v>6593001</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -24762,7 +24776,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24772,7 +24786,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24798,13 +24812,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827770</t>
+          <t>https://artportalen.se/Sighting/122827482</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>122853672</v>
+        <v>122827770</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -24833,19 +24847,16 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Båshöjden, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>476703</v>
+        <v>476775</v>
       </c>
       <c r="R191" t="n">
-        <v>6593133</v>
+        <v>6593103</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -24872,12 +24883,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24886,31 +24907,30 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853672</t>
+          <t>https://artportalen.se/Sighting/122827770</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>122853678</v>
+        <v>122853672</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -24948,10 +24968,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>476700</v>
+        <v>476703</v>
       </c>
       <c r="R192" t="n">
-        <v>6593134</v>
+        <v>6593133</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -25010,38 +25030,38 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853678</t>
+          <t>https://artportalen.se/Sighting/122853672</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>122853683</v>
+        <v>122853678</v>
       </c>
       <c r="B193" t="n">
-        <v>75428</v>
+        <v>79327</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -25054,10 +25074,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>476692</v>
+        <v>476700</v>
       </c>
       <c r="R193" t="n">
-        <v>6593147</v>
+        <v>6593134</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -25116,16 +25136,16 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122853683</t>
+          <t>https://artportalen.se/Sighting/122853678</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>122826361</v>
+        <v>122853683</v>
       </c>
       <c r="B194" t="n">
-        <v>79084</v>
+        <v>75428</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -25133,34 +25153,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Båshöjden, Båshöjden, Vrm</t>
+          <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>476870</v>
+        <v>476692</v>
       </c>
       <c r="R194" t="n">
-        <v>6593000</v>
+        <v>6593147</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -25187,22 +25210,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25211,33 +25224,34 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122826361</t>
+          <t>https://artportalen.se/Sighting/122853683</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>122827273</v>
+        <v>122826361</v>
       </c>
       <c r="B195" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -25245,21 +25259,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -25269,10 +25283,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>476842</v>
+        <v>476870</v>
       </c>
       <c r="R195" t="n">
-        <v>6592963</v>
+        <v>6593000</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -25304,7 +25318,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -25314,7 +25328,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25340,13 +25354,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827273</t>
+          <t>https://artportalen.se/Sighting/122826361</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>122827376</v>
+        <v>122827273</v>
       </c>
       <c r="B196" t="n">
         <v>79946</v>
@@ -25381,10 +25395,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>476815</v>
+        <v>476842</v>
       </c>
       <c r="R196" t="n">
-        <v>6593013</v>
+        <v>6592963</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -25416,7 +25430,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -25426,7 +25440,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25452,16 +25466,16 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122827376</t>
+          <t>https://artportalen.se/Sighting/122827273</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>122826109</v>
+        <v>122827376</v>
       </c>
       <c r="B197" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -25469,21 +25483,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -25493,10 +25507,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>476865</v>
+        <v>476815</v>
       </c>
       <c r="R197" t="n">
-        <v>6592990</v>
+        <v>6593013</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -25528,7 +25542,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -25538,7 +25552,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25564,16 +25578,16 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122826109</t>
+          <t>https://artportalen.se/Sighting/122827376</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122828141</v>
+        <v>122826109</v>
       </c>
       <c r="B198" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -25581,21 +25595,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -25605,10 +25619,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>476735</v>
+        <v>476865</v>
       </c>
       <c r="R198" t="n">
-        <v>6593133</v>
+        <v>6592990</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -25640,7 +25654,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -25650,7 +25664,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25676,51 +25690,51 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122828141</t>
+          <t>https://artportalen.se/Sighting/122826109</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124505050</v>
+        <v>122828141</v>
       </c>
       <c r="B199" t="n">
-        <v>79327</v>
+        <v>79917</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
+          <t>Båshöjden, Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>482221</v>
+        <v>476735</v>
       </c>
       <c r="R199" t="n">
-        <v>6590913</v>
+        <v>6593133</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -25747,22 +25761,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25788,13 +25802,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124505050</t>
+          <t>https://artportalen.se/Sighting/122828141</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>124505147</v>
+        <v>124505050</v>
       </c>
       <c r="B200" t="n">
         <v>79327</v>
@@ -25829,10 +25843,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>482216</v>
+        <v>482221</v>
       </c>
       <c r="R200" t="n">
-        <v>6590937</v>
+        <v>6590913</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -25864,7 +25878,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -25874,7 +25888,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25900,70 +25914,51 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124505147</t>
+          <t>https://artportalen.se/Sighting/124505050</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>124502716</v>
+        <v>124505147</v>
       </c>
       <c r="B201" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>482257</v>
+        <v>482216</v>
       </c>
       <c r="R201" t="n">
-        <v>6590830</v>
+        <v>6590937</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -25995,7 +25990,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -26005,7 +26000,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -26031,13 +26026,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502716</t>
+          <t>https://artportalen.se/Sighting/124505147</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>124502759</v>
+        <v>124502716</v>
       </c>
       <c r="B202" t="n">
         <v>57141</v>
@@ -26091,10 +26086,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>482259</v>
+        <v>482257</v>
       </c>
       <c r="R202" t="n">
-        <v>6590829</v>
+        <v>6590830</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -26126,7 +26121,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -26136,7 +26131,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26162,13 +26157,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502759</t>
+          <t>https://artportalen.se/Sighting/124502716</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>124502785</v>
+        <v>124502759</v>
       </c>
       <c r="B203" t="n">
         <v>57141</v>
@@ -26222,10 +26217,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>482273</v>
+        <v>482259</v>
       </c>
       <c r="R203" t="n">
-        <v>6590828</v>
+        <v>6590829</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -26257,7 +26252,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -26267,7 +26262,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -26293,13 +26288,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502785</t>
+          <t>https://artportalen.se/Sighting/124502759</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>124502909</v>
+        <v>124502785</v>
       </c>
       <c r="B204" t="n">
         <v>57141</v>
@@ -26349,14 +26344,14 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
+          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>482286</v>
+        <v>482273</v>
       </c>
       <c r="R204" t="n">
-        <v>6590831</v>
+        <v>6590828</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -26388,7 +26383,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -26398,7 +26393,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -26424,13 +26419,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124502909</t>
+          <t>https://artportalen.se/Sighting/124502785</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124503058</v>
+        <v>124502909</v>
       </c>
       <c r="B205" t="n">
         <v>57141</v>
@@ -26484,10 +26479,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>482329</v>
+        <v>482286</v>
       </c>
       <c r="R205" t="n">
-        <v>6590870</v>
+        <v>6590831</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -26519,7 +26514,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -26529,7 +26524,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26555,13 +26550,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503058</t>
+          <t>https://artportalen.se/Sighting/124502909</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124503101</v>
+        <v>124503058</v>
       </c>
       <c r="B206" t="n">
         <v>57141</v>
@@ -26606,7 +26601,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -26615,10 +26610,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>482328</v>
+        <v>482329</v>
       </c>
       <c r="R206" t="n">
-        <v>6590871</v>
+        <v>6590870</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -26650,7 +26645,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -26660,7 +26655,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26686,13 +26681,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503101</t>
+          <t>https://artportalen.se/Sighting/124503058</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>124503372</v>
+        <v>124503101</v>
       </c>
       <c r="B207" t="n">
         <v>57141</v>
@@ -26737,7 +26732,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -26746,10 +26741,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>482345</v>
+        <v>482328</v>
       </c>
       <c r="R207" t="n">
-        <v>6590890</v>
+        <v>6590871</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -26781,7 +26776,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -26791,7 +26786,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26817,13 +26812,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503372</t>
+          <t>https://artportalen.se/Sighting/124503101</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124503506</v>
+        <v>124503372</v>
       </c>
       <c r="B208" t="n">
         <v>57141</v>
@@ -26877,10 +26872,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>482356</v>
+        <v>482345</v>
       </c>
       <c r="R208" t="n">
-        <v>6590902</v>
+        <v>6590890</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -26912,7 +26907,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -26922,7 +26917,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -26948,13 +26943,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503506</t>
+          <t>https://artportalen.se/Sighting/124503372</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124503630</v>
+        <v>124503506</v>
       </c>
       <c r="B209" t="n">
         <v>57141</v>
@@ -27008,10 +27003,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>482376</v>
+        <v>482356</v>
       </c>
       <c r="R209" t="n">
-        <v>6590925</v>
+        <v>6590902</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -27043,7 +27038,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -27053,7 +27048,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -27079,13 +27074,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503630</t>
+          <t>https://artportalen.se/Sighting/124503506</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>124503788</v>
+        <v>124503630</v>
       </c>
       <c r="B210" t="n">
         <v>57141</v>
@@ -27139,10 +27134,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>482320</v>
+        <v>482376</v>
       </c>
       <c r="R210" t="n">
-        <v>6590989</v>
+        <v>6590925</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -27174,7 +27169,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -27184,7 +27179,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27210,13 +27205,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503788</t>
+          <t>https://artportalen.se/Sighting/124503630</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>124503881</v>
+        <v>124503788</v>
       </c>
       <c r="B211" t="n">
         <v>57141</v>
@@ -27270,10 +27265,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>482318</v>
+        <v>482320</v>
       </c>
       <c r="R211" t="n">
-        <v>6590992</v>
+        <v>6590989</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -27305,7 +27300,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -27315,7 +27310,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -27341,13 +27336,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503881</t>
+          <t>https://artportalen.se/Sighting/124503788</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>124503939</v>
+        <v>124503881</v>
       </c>
       <c r="B212" t="n">
         <v>57141</v>
@@ -27401,10 +27396,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>482283</v>
+        <v>482318</v>
       </c>
       <c r="R212" t="n">
-        <v>6591027</v>
+        <v>6590992</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -27436,7 +27431,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -27446,7 +27441,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -27472,13 +27467,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124503939</t>
+          <t>https://artportalen.se/Sighting/124503881</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>124504184</v>
+        <v>124503939</v>
       </c>
       <c r="B213" t="n">
         <v>57141</v>
@@ -27523,7 +27518,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -27532,10 +27527,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>482319</v>
+        <v>482283</v>
       </c>
       <c r="R213" t="n">
-        <v>6590941</v>
+        <v>6591027</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -27567,7 +27562,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -27577,7 +27572,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -27603,13 +27598,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504184</t>
+          <t>https://artportalen.se/Sighting/124503939</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>124504203</v>
+        <v>124504184</v>
       </c>
       <c r="B214" t="n">
         <v>57141</v>
@@ -27654,7 +27649,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -27663,10 +27658,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>482320</v>
+        <v>482319</v>
       </c>
       <c r="R214" t="n">
-        <v>6590940</v>
+        <v>6590941</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -27734,13 +27729,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504203</t>
+          <t>https://artportalen.se/Sighting/124504184</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>124504371</v>
+        <v>124504203</v>
       </c>
       <c r="B215" t="n">
         <v>57141</v>
@@ -27797,7 +27792,7 @@
         <v>482320</v>
       </c>
       <c r="R215" t="n">
-        <v>6590938</v>
+        <v>6590940</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -27829,7 +27824,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -27839,12 +27834,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -27870,13 +27860,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504371</t>
+          <t>https://artportalen.se/Sighting/124504203</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>124504472</v>
+        <v>124504371</v>
       </c>
       <c r="B216" t="n">
         <v>57141</v>
@@ -27930,10 +27920,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>482306</v>
+        <v>482320</v>
       </c>
       <c r="R216" t="n">
-        <v>6590920</v>
+        <v>6590938</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -27965,7 +27955,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -27975,7 +27965,12 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -28001,13 +27996,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504472</t>
+          <t>https://artportalen.se/Sighting/124504371</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>124504533</v>
+        <v>124504472</v>
       </c>
       <c r="B217" t="n">
         <v>57141</v>
@@ -28061,10 +28056,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>482316</v>
+        <v>482306</v>
       </c>
       <c r="R217" t="n">
-        <v>6590915</v>
+        <v>6590920</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -28096,7 +28091,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -28106,7 +28101,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -28132,13 +28127,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504533</t>
+          <t>https://artportalen.se/Sighting/124504472</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>124504560</v>
+        <v>124504533</v>
       </c>
       <c r="B218" t="n">
         <v>57141</v>
@@ -28192,10 +28187,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>482303</v>
+        <v>482316</v>
       </c>
       <c r="R218" t="n">
-        <v>6590900</v>
+        <v>6590915</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -28227,7 +28222,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -28237,7 +28232,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -28263,13 +28258,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504560</t>
+          <t>https://artportalen.se/Sighting/124504533</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>124504630</v>
+        <v>124504560</v>
       </c>
       <c r="B219" t="n">
         <v>57141</v>
@@ -28314,7 +28309,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -28323,10 +28318,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>482305</v>
+        <v>482303</v>
       </c>
       <c r="R219" t="n">
-        <v>6590892</v>
+        <v>6590900</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -28358,7 +28353,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -28368,7 +28363,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -28394,13 +28389,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504630</t>
+          <t>https://artportalen.se/Sighting/124504560</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>124504665</v>
+        <v>124504630</v>
       </c>
       <c r="B220" t="n">
         <v>57141</v>
@@ -28445,7 +28440,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -28454,10 +28449,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>482301</v>
+        <v>482305</v>
       </c>
       <c r="R220" t="n">
-        <v>6590884</v>
+        <v>6590892</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -28489,7 +28484,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -28499,7 +28494,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -28525,13 +28520,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504665</t>
+          <t>https://artportalen.se/Sighting/124504630</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>124504729</v>
+        <v>124504665</v>
       </c>
       <c r="B221" t="n">
         <v>57141</v>
@@ -28585,10 +28580,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>482279</v>
+        <v>482301</v>
       </c>
       <c r="R221" t="n">
-        <v>6590867</v>
+        <v>6590884</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -28620,7 +28615,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -28630,7 +28625,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -28656,13 +28651,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504729</t>
+          <t>https://artportalen.se/Sighting/124504665</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>124504787</v>
+        <v>124504729</v>
       </c>
       <c r="B222" t="n">
         <v>57141</v>
@@ -28716,10 +28711,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>482260</v>
+        <v>482279</v>
       </c>
       <c r="R222" t="n">
-        <v>6590864</v>
+        <v>6590867</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -28751,7 +28746,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -28761,7 +28756,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -28787,13 +28782,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504787</t>
+          <t>https://artportalen.se/Sighting/124504729</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>124504889</v>
+        <v>124504787</v>
       </c>
       <c r="B223" t="n">
         <v>57141</v>
@@ -28843,14 +28838,14 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
+          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>482243</v>
+        <v>482260</v>
       </c>
       <c r="R223" t="n">
-        <v>6590887</v>
+        <v>6590864</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -28882,7 +28877,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -28892,7 +28887,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -28918,13 +28913,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504889</t>
+          <t>https://artportalen.se/Sighting/124504787</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>124504938</v>
+        <v>124504889</v>
       </c>
       <c r="B224" t="n">
         <v>57141</v>
@@ -28978,10 +28973,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>482242</v>
+        <v>482243</v>
       </c>
       <c r="R224" t="n">
-        <v>6590889</v>
+        <v>6590887</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -29013,7 +29008,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -29023,7 +29018,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -29049,13 +29044,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124504938</t>
+          <t>https://artportalen.se/Sighting/124504889</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>124541970</v>
+        <v>124504938</v>
       </c>
       <c r="B225" t="n">
         <v>57141</v>
@@ -29105,14 +29100,14 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
+          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>482334</v>
+        <v>482242</v>
       </c>
       <c r="R225" t="n">
-        <v>6590967</v>
+        <v>6590889</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -29139,22 +29134,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -29180,13 +29175,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124541970</t>
+          <t>https://artportalen.se/Sighting/124504938</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>124541985</v>
+        <v>124541970</v>
       </c>
       <c r="B226" t="n">
         <v>57141</v>
@@ -29236,14 +29231,14 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
+          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>482253</v>
+        <v>482334</v>
       </c>
       <c r="R226" t="n">
-        <v>6590827</v>
+        <v>6590967</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -29275,7 +29270,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -29285,7 +29280,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -29311,13 +29306,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124541985</t>
+          <t>https://artportalen.se/Sighting/124541970</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>124541987</v>
+        <v>124541985</v>
       </c>
       <c r="B227" t="n">
         <v>57141</v>
@@ -29371,10 +29366,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>482262</v>
+        <v>482253</v>
       </c>
       <c r="R227" t="n">
-        <v>6590843</v>
+        <v>6590827</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -29406,7 +29401,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -29416,7 +29411,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -29442,13 +29437,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124541987</t>
+          <t>https://artportalen.se/Sighting/124541985</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>124542022</v>
+        <v>124541987</v>
       </c>
       <c r="B228" t="n">
         <v>57141</v>
@@ -29498,14 +29493,14 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
+          <t>Lönnhålsberget, Lönnhålsberget, Vrm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>482299</v>
+        <v>482262</v>
       </c>
       <c r="R228" t="n">
-        <v>6590938</v>
+        <v>6590843</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -29537,7 +29532,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -29547,7 +29542,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -29573,13 +29568,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542022</t>
+          <t>https://artportalen.se/Sighting/124541987</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>124542037</v>
+        <v>124542022</v>
       </c>
       <c r="B229" t="n">
         <v>57141</v>
@@ -29624,7 +29619,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -29633,10 +29628,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>482327</v>
+        <v>482299</v>
       </c>
       <c r="R229" t="n">
-        <v>6590995</v>
+        <v>6590938</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -29668,7 +29663,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -29678,7 +29673,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -29704,13 +29699,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542037</t>
+          <t>https://artportalen.se/Sighting/124542022</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>124542050</v>
+        <v>124542037</v>
       </c>
       <c r="B230" t="n">
         <v>57141</v>
@@ -29755,7 +29750,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -29764,10 +29759,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>482353</v>
+        <v>482327</v>
       </c>
       <c r="R230" t="n">
-        <v>6591028</v>
+        <v>6590995</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -29799,7 +29794,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -29809,7 +29804,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -29835,13 +29830,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542050</t>
+          <t>https://artportalen.se/Sighting/124542037</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>124542071</v>
+        <v>124542050</v>
       </c>
       <c r="B231" t="n">
         <v>57141</v>
@@ -29895,10 +29890,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>482383</v>
+        <v>482353</v>
       </c>
       <c r="R231" t="n">
-        <v>6591056</v>
+        <v>6591028</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -29930,7 +29925,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -29940,7 +29935,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -29966,13 +29961,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542071</t>
+          <t>https://artportalen.se/Sighting/124542050</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>124542155</v>
+        <v>124542071</v>
       </c>
       <c r="B232" t="n">
         <v>57141</v>
@@ -30026,10 +30021,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>482307</v>
+        <v>482383</v>
       </c>
       <c r="R232" t="n">
-        <v>6591054</v>
+        <v>6591056</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -30061,7 +30056,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -30071,7 +30066,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -30097,13 +30092,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542155</t>
+          <t>https://artportalen.se/Sighting/124542071</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>124542177</v>
+        <v>124542155</v>
       </c>
       <c r="B233" t="n">
         <v>57141</v>
@@ -30157,10 +30152,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>482296</v>
+        <v>482307</v>
       </c>
       <c r="R233" t="n">
-        <v>6591064</v>
+        <v>6591054</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -30192,7 +30187,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>06:16</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -30202,7 +30197,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>06:16</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -30228,13 +30223,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542177</t>
+          <t>https://artportalen.se/Sighting/124542155</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>124542187</v>
+        <v>124542177</v>
       </c>
       <c r="B234" t="n">
         <v>57141</v>
@@ -30279,7 +30274,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -30288,10 +30283,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>482254</v>
+        <v>482296</v>
       </c>
       <c r="R234" t="n">
-        <v>6591068</v>
+        <v>6591064</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -30323,7 +30318,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -30333,7 +30328,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -30359,13 +30354,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542187</t>
+          <t>https://artportalen.se/Sighting/124542177</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>124542191</v>
+        <v>124542187</v>
       </c>
       <c r="B235" t="n">
         <v>57141</v>
@@ -30410,7 +30405,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -30419,10 +30414,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>482255</v>
+        <v>482254</v>
       </c>
       <c r="R235" t="n">
-        <v>6591067</v>
+        <v>6591068</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -30454,7 +30449,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -30464,12 +30459,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>06:19</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -30495,13 +30485,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542191</t>
+          <t>https://artportalen.se/Sighting/124542187</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>124542200</v>
+        <v>124542191</v>
       </c>
       <c r="B236" t="n">
         <v>57141</v>
@@ -30555,10 +30545,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>482293</v>
+        <v>482255</v>
       </c>
       <c r="R236" t="n">
-        <v>6591125</v>
+        <v>6591067</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -30590,7 +30580,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -30600,7 +30590,12 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -30626,38 +30621,38 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542200</t>
+          <t>https://artportalen.se/Sighting/124542191</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>124542160</v>
+        <v>124542200</v>
       </c>
       <c r="B237" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -30670,9 +30665,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -30681,10 +30681,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>482222</v>
+        <v>482293</v>
       </c>
       <c r="R237" t="n">
-        <v>6590970</v>
+        <v>6591125</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -30716,7 +30716,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -30752,16 +30752,16 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124542160</t>
+          <t>https://artportalen.se/Sighting/124542200</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>133039898</v>
+        <v>124542160</v>
       </c>
       <c r="B238" t="n">
-        <v>57391</v>
+        <v>58114</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -30769,21 +30769,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>102961</v>
+        <v>103021</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -30803,14 +30803,14 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Fisklösen norr, Fisklösen norr, Vrm</t>
+          <t>Lönnhålsberget, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>480277</v>
+        <v>482222</v>
       </c>
       <c r="R238" t="n">
-        <v>6590888</v>
+        <v>6590970</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -30837,22 +30837,22 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>04:32</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>04:32</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30878,38 +30878,38 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133039898</t>
+          <t>https://artportalen.se/Sighting/124542160</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>132398767</v>
+        <v>133039898</v>
       </c>
       <c r="B239" t="n">
-        <v>57280</v>
+        <v>57391</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100065</v>
+        <v>102961</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -30917,23 +30917,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Bastkulltjärnen, Vrm</t>
+          <t>Fisklösen norr, Fisklösen norr, Vrm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>480848</v>
+        <v>480277</v>
       </c>
       <c r="R239" t="n">
-        <v>6588847</v>
+        <v>6590888</v>
       </c>
       <c r="S239" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -30957,22 +30963,22 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>04:32</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>04:32</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30987,49 +30993,49 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398767</t>
+          <t>https://artportalen.se/Sighting/133039898</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>132398768</v>
+        <v>132398767</v>
       </c>
       <c r="B240" t="n">
-        <v>57585</v>
+        <v>57280</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>102966</v>
+        <v>100065</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -31118,38 +31124,38 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398768</t>
+          <t>https://artportalen.se/Sighting/132398767</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>132398769</v>
+        <v>132398768</v>
       </c>
       <c r="B241" t="n">
-        <v>57969</v>
+        <v>57585</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>102977</v>
+        <v>102966</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -31159,11 +31165,7 @@
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
@@ -31242,33 +31244,33 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398769</t>
+          <t>https://artportalen.se/Sighting/132398768</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>108276498</v>
+        <v>132398769</v>
       </c>
       <c r="B242" t="n">
-        <v>58541</v>
+        <v>57969</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>102987</v>
+        <v>102977</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -31285,23 +31287,23 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
+          <t>Bastkulltjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>480700</v>
+        <v>480848</v>
       </c>
       <c r="R242" t="n">
-        <v>6588844</v>
+        <v>6588847</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -31325,22 +31327,22 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -31355,27 +31357,27 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108276498</t>
+          <t>https://artportalen.se/Sighting/132398769</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>132398772</v>
+        <v>108276498</v>
       </c>
       <c r="B243" t="n">
-        <v>58136</v>
+        <v>58541</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -31383,21 +31385,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103021</v>
+        <v>102987</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -31409,23 +31411,23 @@
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Bastkulltjärnen, Vrm</t>
+          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>480848</v>
+        <v>480700</v>
       </c>
       <c r="R243" t="n">
-        <v>6588847</v>
+        <v>6588844</v>
       </c>
       <c r="S243" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -31449,22 +31451,22 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -31479,82 +31481,77 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Tomas Jonsson</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132398772</t>
+          <t>https://artportalen.se/Sighting/108276498</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>122698999</v>
+        <v>132398772</v>
       </c>
       <c r="B244" t="n">
-        <v>58790</v>
+        <v>58136</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>ex.</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>dvala</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
+          <t>Bastkulltjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>480766</v>
+        <v>480848</v>
       </c>
       <c r="R244" t="n">
-        <v>6588916</v>
+        <v>6588847</v>
       </c>
       <c r="S244" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -31578,22 +31575,22 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -31602,34 +31599,33 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Irene Södergren</t>
+          <t>Tomas Jonsson</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122698999</t>
+          <t>https://artportalen.se/Sighting/132398772</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129091010</v>
+        <v>122698999</v>
       </c>
       <c r="B245" t="n">
-        <v>91872</v>
+        <v>58790</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -31637,37 +31633,54 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5447</v>
+        <v>208245</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>dvala</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Bastkulltjärnen, Bastkulltjärnen, Vrm</t>
+          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>481291</v>
+        <v>480766</v>
       </c>
       <c r="R245" t="n">
-        <v>6589086</v>
+        <v>6588916</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -31691,22 +31704,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -31715,55 +31728,56 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Irene Södergren</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129091010</t>
+          <t>https://artportalen.se/Sighting/122698999</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129091385</v>
+        <v>129091010</v>
       </c>
       <c r="B246" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -31773,10 +31787,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>481127</v>
+        <v>481291</v>
       </c>
       <c r="R246" t="n">
-        <v>6589109</v>
+        <v>6589086</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -31808,7 +31822,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -31818,7 +31832,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -31844,65 +31858,51 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129091385</t>
+          <t>https://artportalen.se/Sighting/129091010</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129091426</v>
+        <v>129091385</v>
       </c>
       <c r="B247" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
+          <t>Bastkulltjärnen, Bastkulltjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q247" t="n">
         <v>481127</v>
       </c>
       <c r="R247" t="n">
-        <v>6589108</v>
+        <v>6589109</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -31934,7 +31934,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -31944,12 +31944,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>Ringbarkning i äldre tall.</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -31975,16 +31970,16 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129091426</t>
+          <t>https://artportalen.se/Sighting/129091385</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129090983</v>
+        <v>129091426</v>
       </c>
       <c r="B248" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31992,21 +31987,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -32030,10 +32025,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>481289</v>
+        <v>481127</v>
       </c>
       <c r="R248" t="n">
-        <v>6589051</v>
+        <v>6589108</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -32065,7 +32060,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -32075,7 +32070,12 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Ringbarkning i äldre tall.</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -32101,16 +32101,16 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129090983</t>
+          <t>https://artportalen.se/Sighting/129091426</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>131577584</v>
+        <v>129090983</v>
       </c>
       <c r="B249" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -32118,21 +32118,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -32147,19 +32147,19 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Stenbotjärnsbäcken, Stenbotjärnsbäcken, Vrm</t>
+          <t>Bastkulltjärn, Karlsdal, NO Kga, Vrm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>480931</v>
+        <v>481289</v>
       </c>
       <c r="R249" t="n">
-        <v>6587529</v>
+        <v>6589051</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -32186,27 +32186,22 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Rejält ringbarkad tall.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -32232,65 +32227,68 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131577584</t>
+          <t>https://artportalen.se/Sighting/129090983</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>54605883</v>
+        <v>131577584</v>
       </c>
       <c r="B250" t="n">
-        <v>96313</v>
+        <v>57975</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>530</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Kärmen, Nrk</t>
+          <t>Stenbotjärnsbäcken, Stenbotjärnsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>485029</v>
+        <v>480931</v>
       </c>
       <c r="R250" t="n">
-        <v>6574808</v>
+        <v>6587529</v>
       </c>
       <c r="S250" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -32304,7 +32302,7 @@
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Värmland</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
@@ -32314,12 +32312,27 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2015-07-16</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Rejält ringbarkad tall.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -32330,95 +32343,80 @@
       </c>
       <c r="AG250" t="b">
         <v>0</v>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
-        </is>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>sten i skyddat läge ganska nära dämmet</t>
-        </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54605883</t>
+          <t>https://artportalen.se/Sighting/131577584</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>86293398</v>
+        <v>54605883</v>
       </c>
       <c r="B251" t="n">
-        <v>110078</v>
+        <v>96313</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>220299</v>
+        <v>530</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Norviken, V om, Nrk</t>
+          <t>Kärmen, Nrk</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>483641</v>
+        <v>485029</v>
       </c>
       <c r="R251" t="n">
-        <v>6573880</v>
+        <v>6574808</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -32440,24 +32438,14 @@
           <t>Karlskoga</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Kar-0070</t>
-        </is>
-      </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
+          <t>2015-07-16</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -32466,70 +32454,70 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
-      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>sten i skyddat läge ganska nära dämmet</t>
         </is>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY251" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86293398</t>
+          <t>https://artportalen.se/Sighting/54605883</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>721992</v>
+        <v>86293398</v>
       </c>
       <c r="B252" t="n">
-        <v>104211</v>
+        <v>110078</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1910</v>
+        <v>220299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -32542,16 +32530,18 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Blomsterhult, 450 m NO om, Nrk</t>
+          <t>Norviken, V om, Nrk</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>486559</v>
+        <v>483641</v>
       </c>
       <c r="R252" t="n">
-        <v>6572552</v>
+        <v>6573880</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -32578,22 +32568,22 @@
       </c>
       <c r="X252" t="inlineStr">
         <is>
-          <t>T-Kar-0152</t>
+          <t>Arkiv-T-Kar-0070</t>
         </is>
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Upptäckt 2009.</t>
+          <t>32 blommande och överblommade stänglar i vägens NV-dike vid koordinat. 13 stänglar ca 60 m N-ut i NV-diket och 5 stänglar ca. 60 M S-ut i NV-diket.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -32602,12 +32592,13 @@
       <c r="AE252" t="b">
         <v>0</v>
       </c>
+      <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="b">
         <v>0</v>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
+          <t>Vägdike. Uppramsat/grävt för ca. 2 år sedan.</t>
         </is>
       </c>
       <c r="AT252" t="inlineStr"/>
@@ -32623,64 +32614,73 @@
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/721992</t>
+          <t>https://artportalen.se/Sighting/86293398</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>125598096</v>
+        <v>721992</v>
       </c>
       <c r="B253" t="n">
-        <v>57950</v>
+        <v>104211</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100049</v>
+        <v>1910</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Kärmsön, Kärmsön, Nrk</t>
+          <t>Blomsterhult, 450 m NO om, Nrk</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>485667</v>
+        <v>486559</v>
       </c>
       <c r="R253" t="n">
-        <v>6572353</v>
+        <v>6572552</v>
       </c>
       <c r="S253" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -32702,29 +32702,24 @@
           <t>Karlskoga</t>
         </is>
       </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>T-Kar-0152</t>
+        </is>
+      </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2009-07-28</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2009-07-28</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Färska hack i högstubbe</t>
+          <t>Upptäckt 2009.</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -32736,55 +32731,39 @@
       <c r="AG253" t="b">
         <v>0</v>
       </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, mestadels  i mittstängen men även på kanterna.</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
-        </is>
-      </c>
-      <c r="AY253" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125598096</t>
+          <t>https://artportalen.se/Sighting/721992</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>54597186</v>
+        <v>125598096</v>
       </c>
       <c r="B254" t="n">
-        <v>96313</v>
+        <v>57950</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32792,48 +32771,42 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>530</v>
+        <v>100049</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(L. ex Dicks.) Myrin</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>L Noren, Nrk</t>
+          <t>Kärmsön, Kärmsön, Nrk</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>484632</v>
+        <v>485667</v>
       </c>
       <c r="R254" t="n">
-        <v>6571731</v>
+        <v>6572353</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -32857,12 +32830,27 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2015-07-14</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Färska hack i högstubbe</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -32874,29 +32862,167 @@
       <c r="AG254" t="b">
         <v>0</v>
       </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>sjöstrand</t>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Per Darell, Liselott Evasdotter</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598096</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>54597186</v>
+      </c>
+      <c r="B255" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>530</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>L Noren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>484632</v>
+      </c>
+      <c r="R255" t="n">
+        <v>6571731</v>
+      </c>
+      <c r="S255" t="n">
+        <v>10</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2015-07-14</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54597186</t>
         </is>
@@ -33157,6 +33283,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3897-2024 artfynd.xlsx
+++ b/artfynd/S 3897-2024 artfynd.xlsx
@@ -23000,7 +23000,7 @@
         <v>135589649</v>
       </c>
       <c r="B176" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
